--- a/AAII_Financials/Yearly/HOMB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HOMB_YR_FIN.xlsx
@@ -732,7 +732,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1068500</v>
+        <v>1070400</v>
       </c>
       <c r="E8" s="3">
         <v>969000</v>
@@ -834,7 +834,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1068500</v>
+        <v>1070400</v>
       </c>
       <c r="E10" s="3">
         <v>969000</v>
@@ -1008,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>900</v>
+        <v>2800</v>
       </c>
       <c r="E14" s="3">
         <v>2000</v>
@@ -1179,7 +1179,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>612700</v>
+        <v>614600</v>
       </c>
       <c r="E18" s="3">
         <v>524300</v>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>641900</v>
+        <v>643800</v>
       </c>
       <c r="E21" s="3">
         <v>553500</v>
